--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -41,7 +41,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="61" x14ac:knownFonts="1">
+  <fonts count="83" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,6 +498,128 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF00B050"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="DecoType Naskh Special"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1105,7 +1227,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="448">
+  <cellXfs count="486">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2424,6 +2546,120 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="65" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2866,128 +3102,128 @@
       <c r="X5" s="236"/>
       <c r="Y5" s="236"/>
     </row>
-    <row r="6" spans="1:25" s="5" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="51" t="inlineStr">
+    <row r="6" spans="1:25" s="5" customFormat="1" ht="39.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="454" t="inlineStr">
         <is>
           <t xml:space="preserve">الولاية</t>
         </is>
       </c>
-      <c r="B6" s="148" t="inlineStr">
+      <c r="B6" s="469" t="inlineStr">
         <is>
           <t xml:space="preserve">م</t>
         </is>
       </c>
-      <c r="C6" s="229" t="inlineStr">
+      <c r="C6" s="482" t="inlineStr">
         <is>
           <t xml:space="preserve">المشرف</t>
         </is>
       </c>
-      <c r="D6" s="199" t="inlineStr">
+      <c r="D6" s="478" t="inlineStr">
         <is>
           <t xml:space="preserve">م مشرف</t>
         </is>
       </c>
-      <c r="E6" s="149" t="inlineStr">
+      <c r="E6" s="470" t="inlineStr">
         <is>
           <t xml:space="preserve">المدرسة </t>
         </is>
       </c>
-      <c r="F6" s="202" t="inlineStr">
+      <c r="F6" s="479" t="inlineStr">
         <is>
           <t xml:space="preserve">القوة </t>
         </is>
       </c>
-      <c r="G6" s="50" t="inlineStr">
+      <c r="G6" s="453" t="inlineStr">
         <is>
           <t xml:space="preserve">رقم الملف</t>
         </is>
       </c>
-      <c r="H6" s="48" t="inlineStr">
+      <c r="H6" s="452" t="inlineStr">
         <is>
           <t xml:space="preserve">الاسم </t>
         </is>
       </c>
-      <c r="I6" s="202" t="inlineStr">
+      <c r="I6" s="479" t="inlineStr">
         <is>
           <t xml:space="preserve">عدد الحصص</t>
         </is>
       </c>
-      <c r="J6" s="102" t="inlineStr">
+      <c r="J6" s="460" t="inlineStr">
         <is>
           <t xml:space="preserve">يدرس فصول</t>
         </is>
       </c>
-      <c r="K6" s="18" t="inlineStr">
+      <c r="K6" s="449" t="inlineStr">
         <is>
           <t xml:space="preserve">ملاحظات </t>
         </is>
       </c>
-      <c r="L6" s="119" t="inlineStr">
+      <c r="L6" s="462" t="inlineStr">
         <is>
           <t xml:space="preserve">الهاتف</t>
         </is>
       </c>
-      <c r="M6" s="102" t="inlineStr">
+      <c r="M6" s="460" t="inlineStr">
         <is>
           <t xml:space="preserve">السكن الحالي</t>
         </is>
       </c>
-      <c r="N6" s="162" t="inlineStr">
+      <c r="N6" s="472" t="inlineStr">
         <is>
           <t xml:space="preserve">اسم مدير المدرسة</t>
         </is>
       </c>
-      <c r="O6" s="121" t="inlineStr">
+      <c r="O6" s="464" t="inlineStr">
         <is>
           <t xml:space="preserve">رقم هاتفه </t>
         </is>
       </c>
-      <c r="P6" s="120" t="inlineStr">
+      <c r="P6" s="463" t="inlineStr">
         <is>
           <t xml:space="preserve">عام التعيين</t>
         </is>
       </c>
-      <c r="Q6" s="102" t="inlineStr">
+      <c r="Q6" s="460" t="inlineStr">
         <is>
           <t xml:space="preserve">الدرجة </t>
         </is>
       </c>
-      <c r="R6" s="51" t="inlineStr">
+      <c r="R6" s="454" t="inlineStr">
         <is>
           <t xml:space="preserve">الرقم المدني</t>
         </is>
       </c>
-      <c r="S6" s="119" t="inlineStr">
+      <c r="S6" s="462" t="inlineStr">
         <is>
           <t xml:space="preserve">الجامعة </t>
         </is>
       </c>
-      <c r="T6" s="167" t="inlineStr">
+      <c r="T6" s="473" t="inlineStr">
         <is>
           <t xml:space="preserve">المؤهل</t>
         </is>
       </c>
-      <c r="U6" s="167" t="inlineStr">
+      <c r="U6" s="473" t="inlineStr">
         <is>
           <t xml:space="preserve">التخصص </t>
         </is>
       </c>
-      <c r="V6" s="51" t="inlineStr">
+      <c r="V6" s="454" t="inlineStr">
         <is>
           <t xml:space="preserve">الحالة الاجتماعية</t>
         </is>
       </c>
-      <c r="W6" s="133" t="inlineStr">
+      <c r="W6" s="467" t="inlineStr">
         <is>
           <t xml:space="preserve">تاريخ الميلاد</t>
         </is>
       </c>
-      <c r="X6" s="50" t="inlineStr">
+      <c r="X6" s="453" t="inlineStr">
         <is>
           <t xml:space="preserve">العنوان الدائم</t>
         </is>
       </c>
-      <c r="Y6" s="51" t="inlineStr">
+      <c r="Y6" s="454" t="inlineStr">
         <is>
           <t xml:space="preserve">البريد الالكتروني</t>
         </is>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -41,7 +41,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="83" x14ac:knownFonts="1">
+  <fonts count="88" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -619,6 +619,34 @@
     <font>
       <b/>
       <sz val="14"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="DecoType Naskh Special"/>
     </font>
   </fonts>
@@ -672,7 +700,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="45">
+  <borders count="46">
     <border>
       <left/>
       <right/>
@@ -1212,6 +1240,21 @@
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1227,7 +1270,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="486">
+  <cellXfs count="511">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2661,6 +2704,81 @@
     </xf>
     <xf numFmtId="0" fontId="82" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -41,7 +41,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="88" x14ac:knownFonts="1">
+  <fonts count="89" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -646,6 +646,11 @@
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="DecoType Naskh Special"/>
     </font>
@@ -1270,7 +1275,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="511">
+  <cellXfs count="512">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2778,6 +2783,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3123,7 +3131,7 @@
     <col min="22" max="22" width="8" style="47" customWidth="1"/>
     <col min="23" max="23" width="10.5703125" style="47" customWidth="1"/>
     <col min="24" max="24" width="10.42578125" style="47" customWidth="1"/>
-    <col min="25" max="25" width="29" style="47" customWidth="1"/>
+    <col min="25" max="25" width="34" style="47" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -41,7 +41,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="89" x14ac:knownFonts="1">
+  <fonts count="90" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -653,6 +653,13 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1275,7 +1282,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="512">
+  <cellXfs count="524">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2786,6 +2793,42 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="88" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -41,7 +41,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="90" x14ac:knownFonts="1">
+  <fonts count="95" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,6 +656,44 @@
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1282,7 +1320,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="524">
+  <cellXfs count="538">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2829,6 +2867,48 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2940,7 +3020,7 @@
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:cs typeface="DecoType Naskh Special"/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -41,7 +41,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="95" x14ac:knownFonts="1">
+  <fonts count="90" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,44 +656,6 @@
     </font>
     <font>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1320,7 +1282,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="538">
+  <cellXfs count="524">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2867,48 +2829,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3020,7 +2940,7 @@
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
-        <a:cs typeface="DecoType Naskh Special"/>
+        <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -41,7 +41,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="90" x14ac:knownFonts="1">
+  <fonts count="95" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,6 +656,44 @@
     </font>
     <font>
       <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1282,7 +1320,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="524">
+  <cellXfs count="538">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2718,46 +2756,46 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2772,22 +2810,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2799,36 +2837,78 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2940,7 +3020,7 @@
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
-        <a:cs typeface=""/>
+        <a:cs typeface="DecoType Naskh Special"/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -41,7 +41,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
   </numFmts>
-  <fonts count="95" x14ac:knownFonts="1">
+  <fonts count="90" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -656,44 +656,6 @@
     </font>
     <font>
       <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="18"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1320,7 +1282,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="538">
+  <cellXfs count="524">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2756,46 +2718,46 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2810,22 +2772,22 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2837,78 +2799,36 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="91" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="94" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3020,7 +2940,7 @@
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
-        <a:cs typeface="DecoType Naskh Special"/>
+        <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -36,8 +36,2830 @@
 </workbook>
 </file>
 
-<file path=xl/styles.xml><?xml version="1.0" encoding="UTF-8" standalone="yes"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac x16r2 xr" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision"><numFmts count="1"><numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/></numFmts><fonts count="95" x14ac:knownFonts="1"><font><sz val="11"/><color theme="1"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><sz val="10"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="8"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="11"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="8"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="12"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="10"/><name val="Arial"/><family val="2"/></font><font><sz val="8"/><name val="Arial"/><family val="2"/></font><font><u/><sz val="10"/><color indexed="12"/><name val="Arial"/><family val="2"/></font><font><b/><sz val="12"/><name val="Arial"/><family val="2"/></font><font><u/><sz val="10"/><color theme="10"/><name val="Arial"/><family val="2"/></font><font><b/><sz val="8"/><color rgb="FFFF0000"/><name val="Arial"/><family val="2"/></font><font><b/><sz val="10"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="8"/><color rgb="FFFF0000"/><name val="Arial"/><family val="2"/></font><font><b/><sz val="9"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="10"/><color rgb="FFFF0000"/><name val="Arial"/><family val="2"/></font><font><sz val="9"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="11"/><color rgb="FFFF0000"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="11"/><color rgb="FF00B050"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="10"/><color rgb="FFFF0000"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="10"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="8"/><color rgb="FFFF0000"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="10"/><name val="Arial"/><family val="2"/></font><font><b/><sz val="10"/><color theme="3" tint="0.39997558519241921"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="10"/><color rgb="FF00B050"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="10"/><color rgb="FFFF0000"/><name val="Arial"/><family val="2"/></font><font><b/><sz val="10"/><color theme="1"/><name val="Arial"/><family val="2"/></font><font><b/><sz val="10"/><color rgb="FF00B0F0"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><sz val="12"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="9"/><color theme="1"/><name val="Arial"/><family val="2"/></font><font><sz val="8"/><color theme="1"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="8"/><color rgb="FF00B050"/><name val="Arial"/><family val="2"/></font><font><b/><sz val="8"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="11"/><color theme="3" tint="0.39997558519241921"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="9"/><color theme="1"/><name val="Cambria"/><family val="1"/><scheme val="major"/></font><font><sz val="9"/><name val="Cambria"/><family val="1"/><scheme val="major"/></font><font><b/><sz val="8"/><color theme="1"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="8"/><color theme="1"/><name val="Arial"/><family val="2"/><charset val="178"/></font><font><sz val="8"/><name val="Arial"/><family val="2"/><charset val="178"/></font><font><sz val="12"/><color rgb="FF00B0F0"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><sz val="12"/><color theme="1"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="12"/><color theme="1"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="12"/><color theme="3" tint="0.39997558519241921"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><sz val="12"/><color rgb="FFFF0000"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="12"/><color rgb="FFFF0000"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="12"/><color rgb="FF00B0F0"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="8"/><color rgb="FF0070C0"/><name val="Arial"/><family val="2"/></font><font><b/><sz val="8"/><color rgb="FF0070C0"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="14"/><color rgb="FF0070C0"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="22"/><color rgb="FF0070C0"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="12"/><color rgb="FFFF0000"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="20"/><color rgb="FFFF0000"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><b/><sz val="10"/><color theme="1"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="8"/><color theme="3" tint="0.39997558519241921"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="9"/><color rgb="FFFF0000"/><name val="Cambria"/><family val="1"/><scheme val="major"/></font><font><b/><sz val="8"/><color rgb="FFFF0000"/><name val="Arial"/><family val="2"/><charset val="178"/></font><font><sz val="11"/><color rgb="FFFF0000"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="10"/><color rgb="FFFF0000"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><b/><sz val="12"/><color rgb="FFFF0000"/><name val="Arial"/><family val="2"/></font><font><sz val="8"/><color rgb="FFFF0000"/><name val="Calibri"/><family val="2"/><charset val="178"/><scheme val="minor"/></font><font><sz val="8"/><color rgb="FFFF0000"/><name val="Arial"/><family val="2"/><charset val="178"/></font><font><b/><sz val="16"/><color rgb="FF00B050"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><sz val="16"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="16"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="16"/><color theme="3" tint="0.39997558519241921"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="14"/><color rgb="FFFF0000"/><name val="DecoType Naskh Special"/></font><font><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><sz val="14"/><name val="DecoType Naskh Special"/></font><font><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="16"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="18"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="18"/><color rgb="FFFF0000"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="18"/><color theme="3" tint="0.39997558519241921"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="14"/><color rgb="FF0070C0"/><name val="DecoType Naskh Special"/></font><font><b/><sz val="14"/><name val="DecoType Naskh Special"/></font><font><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/><b/></font><font><sz val="18"/><color theme="1"/><name val="DecoType Naskh Special"/><b/></font><font><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/><b/></font><font><sz val="16"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><sz val="14"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><sz val="12"/><color theme="1"/><name val="DecoType Naskh Special"/></font><font><sz val="14"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="16"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/><b/></font><font><sz val="18"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/><b/></font><font><sz val="14"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/><b/></font><font><sz val="14"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font><font><sz val="16"/><color theme="1"/><name val="Calibri"/><family val="2"/><scheme val="minor"/></font></fonts><fills count="9"><fill><patternFill patternType="none"/></fill><fill><patternFill patternType="gray125"/></fill><fill><patternFill patternType="solid"><fgColor theme="0"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor rgb="FF92D050"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor theme="3" tint="0.79998168889431442"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor theme="8" tint="0.79998168889431442"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor theme="6" tint="0.79998168889431442"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor theme="9" tint="0.79998168889431442"/><bgColor indexed="64"/></patternFill></fill><fill><patternFill patternType="solid"><fgColor theme="4" tint="0.79998168889431442"/><bgColor indexed="64"/></patternFill></fill></fills><borders count="46"><border><left/><right/><top/><bottom/><diagonal/></border><border><left style="thin"><color indexed="64"/></left><right style="thin"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thin"><color indexed="64"/></left><right style="thin"><color indexed="64"/></right><top/><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left/><right style="thin"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom/><diagonal/></border><border><left/><right style="thin"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left/><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left/><right style="thick"><color indexed="64"/></right><top/><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left/><right style="thick"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top style="thin"><color indexed="64"/></top><bottom/><diagonal/></border><border><left/><right/><top/><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top/><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left/><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left/><right/><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left/><right/><top style="thick"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left/><right/><top style="thin"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left/><right/><top style="thin"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left/><right/><top/><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left/><right style="thick"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top/><bottom/><diagonal/></border><border><left/><right/><top style="thin"><color indexed="64"/></top><bottom/><diagonal/></border><border><left/><right style="thick"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom/><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom/><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top style="thin"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top/><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top style="thin"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top/><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left/><right style="thick"><color indexed="64"/></right><top/><bottom/><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top/><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top style="thick"><color indexed="64"/></top><bottom/><diagonal/></border><border><left style="thin"><color indexed="64"/></left><right style="thin"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thin"><color indexed="64"/></left><right style="thin"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top style="thick"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right/><top/><bottom/><diagonal/></border><border><left/><right style="thick"><color indexed="64"/></right><top/><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border><border><left/><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom/><diagonal/></border><border><left/><right style="thin"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thin"><color indexed="64"/></bottom><diagonal/></border><border><left style="thin"><color indexed="64"/></left><right style="thin"><color indexed="64"/></right><top style="thin"><color indexed="64"/></top><bottom/><diagonal/></border><border><left/><right/><top style="thick"><color indexed="64"/></top><bottom/><diagonal/></border><border><left style="thin"><color indexed="64"/></left><right style="thin"><color indexed="64"/></right><top/><bottom/><diagonal/></border><border><left style="thick"><color indexed="64"/></left><right style="thick"><color indexed="64"/></right><top style="thick"><color indexed="64"/></top><bottom style="thick"><color indexed="64"/></bottom><diagonal/></border></borders><cellStyleXfs count="4"><xf numFmtId="0" fontId="0" fillId="0" borderId="0"/><xf numFmtId="0" fontId="6" fillId="0" borderId="0"/><xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"><alignment vertical="top"/><protection locked="0"/></xf><xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"><alignment vertical="top"/><protection locked="0"/></xf></cellStyleXfs><cellXfs count="540"><xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/><xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/><xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/><xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/><xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/><xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="12" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/><xf numFmtId="0" fontId="20" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="14" fontId="6" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="14" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="20" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="20" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="20" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="14" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="20" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="12" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="16" fontId="26" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="16" fontId="26" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="16" fontId="26" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="16" fontId="26" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="31" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="12" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1"><alignment horizontal="center"/><xf numFmtId="14" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="26" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="26" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="4" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="27" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="27" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="26" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="32" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/><xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="12" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="14" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="27" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"><alignment vertical="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="12" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="21" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="27" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="16" fontId="26" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="34" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="34" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="34" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="35" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="35" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="35" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="36" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="37" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="38" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="38" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="38" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="38" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="38" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="25" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="25" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="35" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="25" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="25" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="25" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="39" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="22" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="24" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="24" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="22" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="22" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="22" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="41" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="42" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="44" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="39" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="39" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="42" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="45" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="45" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="45" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="45" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="45" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="42" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="45" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="46" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="46" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="46" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="46" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="46" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="47" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="47" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="37" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="38" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="20" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="16" fontId="26" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="37" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="40" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="43" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="41" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="41" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="52" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="52" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="20" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="20" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/><xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/><xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="21" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="53" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="52" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="47" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="20" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="20" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="24" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="14" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1"><alignment horizontal="center"/><xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="25" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="25" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="25" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="43" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="14" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/><xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="56" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="54" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="54" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="44" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="54" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="16" fontId="25" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="55" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="55" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="56" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="14" fontId="19" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="56" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/><xf numFmtId="0" fontId="56" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/><xf numFmtId="0" fontId="54" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="54" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="55" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="56" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="44" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="54" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="60" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="164" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="22" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="35" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="60" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="27" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="25" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="16" fontId="25" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="55" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="25" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="43" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="25" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="16" fontId="25" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="55" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="54" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="55" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="55" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="14" fontId="19" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="37" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="46" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="40" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="25" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="26" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="34" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="20" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="37" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="55" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="34" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="54" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="16" fontId="25" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="55" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="39" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="39" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="20" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="39" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="16" fontId="26" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="26" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="58" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="54" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="56" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="59" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="59" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="56" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="35" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="14" fontId="20" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="11" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="57" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="46" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="45" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="25" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="14" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="16" fontId="26" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="28" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="61" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="62" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="14" fontId="63" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="64" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="62" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="62" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="16" fontId="65" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="64" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="66" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="62" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="65" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="67" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="68" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="62" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="69" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="67" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="64" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="70" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="62" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="62" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="71" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="72" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="72" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="73" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="74" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="75" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="76" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="77" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="78" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="79" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="80" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="81" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center"/><xf numFmtId="0" fontId="62" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="78" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" readingOrder="2"/><xf numFmtId="0" fontId="67" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="82" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="88" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center"/><xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="91" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="94" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="94" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" wrapText="1"/><xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/><xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"><alignment horizontal="center" vertical="center" readingOrder="2"/></cellXfs><cellStyles count="4"><cellStyle name="Hyperlink_ورقة1_1" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/><cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/><cellStyle name="ارتباط تشعبي" xfId="2" builtinId="8"/><cellStyle name="عادي" xfId="0" builtinId="0"/></cellStyles><dxfs count="0"/><tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/><colors><mruColors><color rgb="FFFF00FF"/></mruColors></colors><extLst><ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main"><x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/></ext><ext uri="{9260A510-F301-46a8-8635-F512D64BE5F5}" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main"><x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/></ext></extLst></styleSheet>
+<file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
+  </numFmts>
+  <fonts count="90" x14ac:knownFonts="1">
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color indexed="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color theme="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF00B050"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FF0070C0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="178"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <charset val="178"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF00B050"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFF0000"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3" tint="0.39997558519241921"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+      <b/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="DecoType Naskh Special"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+  </fonts>
+  <fills count="9">
+    <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+  </fills>
+  <borders count="46">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color indexed="64"/>
+      </left>
+      <right style="thick">
+        <color indexed="64"/>
+      </right>
+      <top style="thick">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thick">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+  </borders>
+  <cellStyleXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+  </cellStyleXfs>
+  <cellXfs count="526">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="26" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="16" fontId="26" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="16" fontId="26" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="16" fontId="26" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="31" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="32" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="16" fontId="26" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="26" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="53" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="47" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="25" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="25" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="16" fontId="25" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="19" fillId="2" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="16" fontId="25" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="55" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="16" fontId="26" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="7" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="59" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="56" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="57" fillId="6" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="16" fontId="26" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="50" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="63" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="16" fontId="65" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="66" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="68" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="64" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="63" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="73" fillId="5" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="79" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="62" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="67" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+  </cellXfs>
+  <cellStyles count="4">
+    <cellStyle name="Hyperlink_ورقة1_1" xfId="3" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
+    <cellStyle name="ارتباط تشعبي" xfId="2" builtinId="8"/>
+    <cellStyle name="عادي" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF00FF"/>
+    </mruColors>
+  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
+</styleSheet>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -124,7 +2946,7 @@
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
-        <a:cs typeface="DecoType Naskh Special"/>
+        <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
         <a:font script="Hans" typeface="宋体"/>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -38,8 +38,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="90" x14ac:knownFonts="1">
     <font>
@@ -1282,7 +1283,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="526">
+  <cellXfs count="527">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2835,6 +2836,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="165" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -42,7 +42,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="90" x14ac:knownFonts="1">
+  <fonts count="91" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -661,6 +661,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color rgb="FF00B050"/>
+      <name val="DecoType Naskh Special"/>
     </font>
   </fonts>
   <fills count="9">
@@ -1283,7 +1289,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="527">
+  <cellXfs count="544">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2839,6 +2845,57 @@
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
     <xf applyNumberFormat="1" numFmtId="165" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="165" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>
@@ -3166,15 +3223,15 @@
     <col min="4" max="4" width="3.7109375" style="198" customWidth="1"/>
     <col min="5" max="5" width="21" style="152" customWidth="1"/>
     <col min="6" max="6" width="4.42578125" style="201" customWidth="1"/>
-    <col min="7" max="7" width="12" style="47" customWidth="1"/>
+    <col min="7" max="7" width="13.5" style="47" customWidth="1"/>
     <col min="8" max="8" width="23.7109375" style="49" customWidth="1"/>
     <col min="9" max="9" width="4.7109375" style="214" customWidth="1"/>
     <col min="10" max="10" width="8" style="47" customWidth="1"/>
     <col min="11" max="11" width="8.42578125" style="14" customWidth="1"/>
-    <col min="12" max="12" width="13.0" style="47" customWidth="1"/>
+    <col min="12" max="12" width="15.0" style="47" customWidth="1"/>
     <col min="13" max="13" width="8.5703125" style="46" customWidth="1"/>
     <col min="14" max="14" width="15.7109375" style="160" customWidth="1"/>
-    <col min="15" max="15" width="13.0" style="47" customWidth="1"/>
+    <col min="15" max="15" width="14.0" style="47" customWidth="1"/>
     <col min="16" max="16" width="8.28515625" style="47" customWidth="1"/>
     <col min="17" max="17" width="9.28515625" style="47" customWidth="1"/>
     <col min="18" max="18" width="18.7109375" style="47" customWidth="1"/>
@@ -3182,7 +3239,7 @@
     <col min="20" max="20" width="13.42578125" style="166" customWidth="1"/>
     <col min="21" max="21" width="8.42578125" style="166" customWidth="1"/>
     <col min="22" max="22" width="8" style="47" customWidth="1"/>
-    <col min="23" max="23" width="10.5703125" style="47" customWidth="1"/>
+    <col min="23" max="23" width="15.0" style="47" customWidth="1"/>
     <col min="24" max="24" width="10.42578125" style="47" customWidth="1"/>
     <col min="25" max="25" width="34" style="47" customWidth="1"/>
   </cols>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -504,156 +504,156 @@
       <b/>
       <sz val="16"/>
       <color rgb="FF00B050"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <sz val="16"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="3" tint="0.39997558519241921"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <sz val="14"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FFFF0000"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="3" tint="0.39997558519241921"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF0070C0"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <b/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <b/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
       <b/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
     <font>
       <sz val="14"/>
@@ -666,7 +666,7 @@
       <b/>
       <sz val="20"/>
       <color rgb="FF00B050"/>
-      <name val="DecoType Naskh Special"/>
+      <name val="Traditional Arabic"/>
     </font>
   </fonts>
   <fills count="9">

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -504,156 +504,156 @@
       <b/>
       <sz val="16"/>
       <color rgb="FF00B050"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="16"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="3" tint="0.39997558519241921"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="14"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="16"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color rgb="FFFF0000"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="18"/>
       <color theme="3" tint="0.39997558519241921"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color rgb="FF0070C0"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <b/>
     </font>
     <font>
       <sz val="18"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <b/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
       <b/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
     <font>
       <sz val="14"/>
@@ -666,7 +666,7 @@
       <b/>
       <sz val="20"/>
       <color rgb="FF00B050"/>
-      <name val="Traditional Arabic"/>
+      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="9">
@@ -3228,10 +3228,10 @@
     <col min="9" max="9" width="4.7109375" style="214" customWidth="1"/>
     <col min="10" max="10" width="8" style="47" customWidth="1"/>
     <col min="11" max="11" width="8.42578125" style="14" customWidth="1"/>
-    <col min="12" max="12" width="15.0" style="47" customWidth="1"/>
+    <col min="12" max="12" width="17.0" style="47" customWidth="1"/>
     <col min="13" max="13" width="8.5703125" style="46" customWidth="1"/>
     <col min="14" max="14" width="15.7109375" style="160" customWidth="1"/>
-    <col min="15" max="15" width="14.0" style="47" customWidth="1"/>
+    <col min="15" max="15" width="15.5" style="47" customWidth="1"/>
     <col min="16" max="16" width="8.28515625" style="47" customWidth="1"/>
     <col min="17" max="17" width="9.28515625" style="47" customWidth="1"/>
     <col min="18" max="18" width="18.7109375" style="47" customWidth="1"/>
@@ -3239,7 +3239,7 @@
     <col min="20" max="20" width="13.42578125" style="166" customWidth="1"/>
     <col min="21" max="21" width="8.42578125" style="166" customWidth="1"/>
     <col min="22" max="22" width="8" style="47" customWidth="1"/>
-    <col min="23" max="23" width="15.0" style="47" customWidth="1"/>
+    <col min="23" max="23" width="17.0" style="47" customWidth="1"/>
     <col min="24" max="24" width="10.42578125" style="47" customWidth="1"/>
     <col min="25" max="25" width="34" style="47" customWidth="1"/>
   </cols>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -42,7 +42,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="91" x14ac:knownFonts="1">
+  <fonts count="92" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -665,6 +665,12 @@
     <font>
       <b/>
       <sz val="20"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
       <color rgb="FF00B050"/>
       <name val="Arial"/>
     </font>
@@ -1289,7 +1295,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="544">
+  <cellXfs count="550">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2896,6 +2902,24 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf applyNumberFormat="1" numFmtId="165" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
     </xf>
   </cellXfs>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -1295,7 +1295,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="550">
+  <cellXfs count="559">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2921,6 +2921,33 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf applyNumberFormat="1" numFmtId="165" fontId="61" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -42,7 +42,7 @@
     <numFmt numFmtId="164" formatCode="[$-1010000]yyyy/mm/dd;@"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="92" x14ac:knownFonts="1">
+  <fonts count="96" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -671,6 +671,30 @@
     <font>
       <b/>
       <sz val="18"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <b/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color rgb="FF00B050"/>
       <name val="Arial"/>
     </font>
@@ -1295,7 +1319,7 @@
       <protection locked="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="559">
+  <cellXfs count="563">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2947,6 +2971,18 @@
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" readingOrder="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="95" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" readingOrder="2"/>
     </xf>
   </cellXfs>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -3304,31 +3304,31 @@
   <dimension ref="A1:AF6"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.85546875" style="47" customWidth="1"/>
-    <col min="2" max="2" width="4.140625" style="4" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" style="47" customWidth="1"/>
-    <col min="4" max="4" width="3.7109375" style="198" customWidth="1"/>
-    <col min="5" max="5" width="21" style="152" customWidth="1"/>
-    <col min="6" max="6" width="4.42578125" style="201" customWidth="1"/>
-    <col min="7" max="7" width="13.5" style="47" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" style="49" customWidth="1"/>
-    <col min="9" max="9" width="4.7109375" style="214" customWidth="1"/>
-    <col min="10" max="10" width="8" style="47" customWidth="1"/>
-    <col min="11" max="11" width="8.42578125" style="14" customWidth="1"/>
+    <col min="1" max="1" width="11.3" style="47" customWidth="1"/>
+    <col min="2" max="2" width="4.14" style="4" customWidth="1"/>
+    <col min="3" max="3" width="24.3" style="47" customWidth="1"/>
+    <col min="4" max="4" width="3.71" style="198" customWidth="1"/>
+    <col min="5" max="5" width="60.0" style="152" customWidth="1"/>
+    <col min="6" max="6" width="4.43" style="201" customWidth="1"/>
+    <col min="7" max="7" width="15.3" style="47" customWidth="1"/>
+    <col min="8" max="8" width="41.7" style="49" customWidth="1"/>
+    <col min="9" max="9" width="4.71" style="214" customWidth="1"/>
+    <col min="10" max="10" width="24.3" style="47" customWidth="1"/>
+    <col min="11" max="11" width="8.43" style="14" customWidth="1"/>
     <col min="12" max="12" width="17.0" style="47" customWidth="1"/>
-    <col min="13" max="13" width="8.5703125" style="46" customWidth="1"/>
-    <col min="14" max="14" width="15.7109375" style="160" customWidth="1"/>
+    <col min="13" max="13" width="45.7" style="46" customWidth="1"/>
+    <col min="14" max="14" width="38.1" style="160" customWidth="1"/>
     <col min="15" max="15" width="15.5" style="47" customWidth="1"/>
-    <col min="16" max="16" width="8.28515625" style="47" customWidth="1"/>
-    <col min="17" max="17" width="9.28515625" style="47" customWidth="1"/>
-    <col min="18" max="18" width="18.7109375" style="47" customWidth="1"/>
-    <col min="19" max="19" width="13.42578125" style="47" customWidth="1"/>
-    <col min="20" max="20" width="13.42578125" style="166" customWidth="1"/>
-    <col min="21" max="21" width="8.42578125" style="166" customWidth="1"/>
-    <col min="22" max="22" width="8" style="47" customWidth="1"/>
+    <col min="16" max="16" width="8.9" style="47" customWidth="1"/>
+    <col min="17" max="17" width="9.29" style="47" customWidth="1"/>
+    <col min="18" max="18" width="18.71" style="47" customWidth="1"/>
+    <col min="19" max="19" width="52.1" style="47" customWidth="1"/>
+    <col min="20" max="20" width="56.1" style="166" customWidth="1"/>
+    <col min="21" max="21" width="41.5" style="166" customWidth="1"/>
+    <col min="22" max="22" width="10.5" style="47" customWidth="1"/>
     <col min="23" max="23" width="17.0" style="47" customWidth="1"/>
-    <col min="24" max="24" width="10.42578125" style="47" customWidth="1"/>
-    <col min="25" max="25" width="34" style="47" customWidth="1"/>
+    <col min="24" max="24" width="53.7" style="47" customWidth="1"/>
+    <col min="25" max="25" width="34.0" style="47" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">ورقة1!$A$6:$BM$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">ورقة1!$B$6:$Y$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">ورقة1!$B$6:$Z$6</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -3329,6 +3329,7 @@
     <col min="23" max="23" width="17.0" style="47" customWidth="1"/>
     <col min="24" max="24" width="53.7" style="47" customWidth="1"/>
     <col min="25" max="25" width="34.0" style="47" customWidth="1"/>
+    <col min="26" max="26" width="14.0" style="47" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -3394,7 +3395,7 @@
       <c r="W4" s="447"/>
       <c r="X4" s="447"/>
     </row>
-    <row r="5" spans="1:25" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:26" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="236"/>
       <c r="B5" s="250"/>
       <c r="C5" s="236"/>
@@ -3424,8 +3425,9 @@
       <c r="W5" s="236"/>
       <c r="X5" s="236"/>
       <c r="Y5" s="236"/>
+      <c r="Z5" s="236"/>
     </row>
-    <row r="6" spans="1:25" s="5" customFormat="1" ht="39.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:26" s="5" customFormat="1" ht="39.95" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="454" t="inlineStr">
         <is>
           <t xml:space="preserve">الولاية</t>
@@ -3549,6 +3551,11 @@
       <c r="Y6" s="454" t="inlineStr">
         <is>
           <t xml:space="preserve">البريد الالكتروني</t>
+        </is>
+      </c>
+      <c r="Z6" s="454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الجنسية</t>
         </is>
       </c>
     </row>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -3312,24 +3312,24 @@
     <col min="6" max="6" width="4.43" style="201" customWidth="1"/>
     <col min="7" max="7" width="15.3" style="47" customWidth="1"/>
     <col min="8" max="8" width="41.7" style="49" customWidth="1"/>
-    <col min="9" max="9" width="4.71" style="214" customWidth="1"/>
-    <col min="10" max="10" width="24.3" style="47" customWidth="1"/>
-    <col min="11" max="11" width="8.43" style="14" customWidth="1"/>
-    <col min="12" max="12" width="17.0" style="47" customWidth="1"/>
-    <col min="13" max="13" width="45.7" style="46" customWidth="1"/>
-    <col min="14" max="14" width="38.1" style="160" customWidth="1"/>
-    <col min="15" max="15" width="15.5" style="47" customWidth="1"/>
-    <col min="16" max="16" width="8.9" style="47" customWidth="1"/>
-    <col min="17" max="17" width="9.29" style="47" customWidth="1"/>
-    <col min="18" max="18" width="18.71" style="47" customWidth="1"/>
-    <col min="19" max="19" width="52.1" style="47" customWidth="1"/>
-    <col min="20" max="20" width="56.1" style="166" customWidth="1"/>
-    <col min="21" max="21" width="41.5" style="166" customWidth="1"/>
-    <col min="22" max="22" width="10.5" style="47" customWidth="1"/>
-    <col min="23" max="23" width="17.0" style="47" customWidth="1"/>
-    <col min="24" max="24" width="53.7" style="47" customWidth="1"/>
-    <col min="25" max="25" width="34.0" style="47" customWidth="1"/>
-    <col min="26" max="26" width="14.0" style="47" customWidth="1"/>
+    <col min="9" max="9" width="14.0" style="47" customWidth="1"/>
+    <col min="10" max="10" width="4.71" style="214" customWidth="1"/>
+    <col min="11" max="11" width="24.3" style="47" customWidth="1"/>
+    <col min="12" max="12" width="8.43" style="14" customWidth="1"/>
+    <col min="13" max="13" width="17.0" style="47" customWidth="1"/>
+    <col min="14" max="14" width="45.7" style="46" customWidth="1"/>
+    <col min="15" max="15" width="38.1" style="160" customWidth="1"/>
+    <col min="16" max="16" width="15.5" style="47" customWidth="1"/>
+    <col min="17" max="17" width="8.9" style="47" customWidth="1"/>
+    <col min="18" max="18" width="9.29" style="47" customWidth="1"/>
+    <col min="19" max="19" width="18.71" style="47" customWidth="1"/>
+    <col min="20" max="20" width="52.1" style="47" customWidth="1"/>
+    <col min="21" max="21" width="56.1" style="166" customWidth="1"/>
+    <col min="22" max="22" width="41.5" style="166" customWidth="1"/>
+    <col min="23" max="23" width="10.5" style="47" customWidth="1"/>
+    <col min="24" max="24" width="17.0" style="47" customWidth="1"/>
+    <col min="25" max="25" width="53.7" style="47" customWidth="1"/>
+    <col min="26" max="26" width="34.0" style="47" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" x14ac:dyDescent="0.25">
@@ -3343,7 +3343,6 @@
 للعام الدراسي (2025م- 2026م)</t>
         </is>
       </c>
-      <c r="I2" s="443"/>
       <c r="J2" s="443"/>
       <c r="K2" s="443"/>
       <c r="L2" s="443"/>
@@ -3353,11 +3352,11 @@
       <c r="P2" s="443"/>
       <c r="Q2" s="443"/>
       <c r="R2" s="443"/>
+      <c r="S2" s="443"/>
     </row>
     <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B3" s="249"/>
       <c r="H3" s="443"/>
-      <c r="I3" s="443"/>
       <c r="J3" s="443"/>
       <c r="K3" s="443"/>
       <c r="L3" s="443"/>
@@ -3367,11 +3366,11 @@
       <c r="P3" s="443"/>
       <c r="Q3" s="443"/>
       <c r="R3" s="443"/>
+      <c r="S3" s="443"/>
     </row>
     <row r="4" spans="1:25" ht="18.75" x14ac:dyDescent="0.25">
       <c r="B4" s="249"/>
       <c r="H4" s="443"/>
-      <c r="I4" s="443"/>
       <c r="J4" s="443"/>
       <c r="K4" s="443"/>
       <c r="L4" s="443"/>
@@ -3381,19 +3380,20 @@
       <c r="P4" s="443"/>
       <c r="Q4" s="443"/>
       <c r="R4" s="443"/>
-      <c r="S4" s="445" t="inlineStr">
+      <c r="S4" s="443"/>
+      <c r="T4" s="445" t="inlineStr">
         <is>
           <t xml:space="preserve">نسخة / نجيب المشايخي </t>
         </is>
       </c>
-      <c r="T4" s="446"/>
-      <c r="V4" s="447" t="inlineStr">
+      <c r="U4" s="446"/>
+      <c r="W4" s="447" t="inlineStr">
         <is>
           <t xml:space="preserve">آخر تحديث: 13/ 10 /2024م</t>
         </is>
       </c>
-      <c r="W4" s="447"/>
       <c r="X4" s="447"/>
+      <c r="Y4" s="447"/>
     </row>
     <row r="5" spans="1:26" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="236"/>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="G5" s="236"/>
       <c r="H5" s="444"/>
-      <c r="I5" s="444"/>
+      <c r="I5" s="236"/>
       <c r="J5" s="444"/>
       <c r="K5" s="444"/>
       <c r="L5" s="444"/>
@@ -3418,10 +3418,10 @@
       <c r="P5" s="444"/>
       <c r="Q5" s="444"/>
       <c r="R5" s="444"/>
-      <c r="S5" s="236"/>
-      <c r="T5" s="237"/>
+      <c r="S5" s="444"/>
+      <c r="T5" s="236"/>
       <c r="U5" s="237"/>
-      <c r="V5" s="236"/>
+      <c r="V5" s="237"/>
       <c r="W5" s="236"/>
       <c r="X5" s="236"/>
       <c r="Y5" s="236"/>
@@ -3468,103 +3468,103 @@
           <t xml:space="preserve">الاسم </t>
         </is>
       </c>
-      <c r="I6" s="479" t="inlineStr">
+      <c r="I6" s="454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">الجنسية</t>
+        </is>
+      </c>
+      <c r="J6" s="479" t="inlineStr">
         <is>
           <t xml:space="preserve">عدد الحصص</t>
         </is>
       </c>
-      <c r="J6" s="460" t="inlineStr">
+      <c r="K6" s="460" t="inlineStr">
         <is>
           <t xml:space="preserve">يدرس فصول</t>
         </is>
       </c>
-      <c r="K6" s="449" t="inlineStr">
+      <c r="L6" s="449" t="inlineStr">
         <is>
           <t xml:space="preserve">ملاحظات </t>
         </is>
       </c>
-      <c r="L6" s="462" t="inlineStr">
+      <c r="M6" s="462" t="inlineStr">
         <is>
           <t xml:space="preserve">الهاتف</t>
         </is>
       </c>
-      <c r="M6" s="460" t="inlineStr">
+      <c r="N6" s="460" t="inlineStr">
         <is>
           <t xml:space="preserve">السكن الحالي</t>
         </is>
       </c>
-      <c r="N6" s="472" t="inlineStr">
+      <c r="O6" s="472" t="inlineStr">
         <is>
           <t xml:space="preserve">اسم مدير المدرسة</t>
         </is>
       </c>
-      <c r="O6" s="464" t="inlineStr">
+      <c r="P6" s="464" t="inlineStr">
         <is>
           <t xml:space="preserve">رقم هاتفه </t>
         </is>
       </c>
-      <c r="P6" s="463" t="inlineStr">
+      <c r="Q6" s="463" t="inlineStr">
         <is>
           <t xml:space="preserve">عام التعيين</t>
         </is>
       </c>
-      <c r="Q6" s="460" t="inlineStr">
+      <c r="R6" s="460" t="inlineStr">
         <is>
           <t xml:space="preserve">الدرجة </t>
         </is>
       </c>
-      <c r="R6" s="454" t="inlineStr">
+      <c r="S6" s="454" t="inlineStr">
         <is>
           <t xml:space="preserve">الرقم المدني</t>
         </is>
       </c>
-      <c r="S6" s="462" t="inlineStr">
+      <c r="T6" s="462" t="inlineStr">
         <is>
           <t xml:space="preserve">الجامعة </t>
         </is>
       </c>
-      <c r="T6" s="473" t="inlineStr">
+      <c r="U6" s="473" t="inlineStr">
         <is>
           <t xml:space="preserve">المؤهل</t>
         </is>
       </c>
-      <c r="U6" s="473" t="inlineStr">
+      <c r="V6" s="473" t="inlineStr">
         <is>
           <t xml:space="preserve">التخصص </t>
         </is>
       </c>
-      <c r="V6" s="454" t="inlineStr">
+      <c r="W6" s="454" t="inlineStr">
         <is>
           <t xml:space="preserve">الحالة الاجتماعية</t>
         </is>
       </c>
-      <c r="W6" s="467" t="inlineStr">
+      <c r="X6" s="467" t="inlineStr">
         <is>
           <t xml:space="preserve">تاريخ الميلاد</t>
         </is>
       </c>
-      <c r="X6" s="453" t="inlineStr">
+      <c r="Y6" s="453" t="inlineStr">
         <is>
           <t xml:space="preserve">العنوان الدائم</t>
         </is>
       </c>
-      <c r="Y6" s="454" t="inlineStr">
+      <c r="Z6" s="454" t="inlineStr">
         <is>
           <t xml:space="preserve">البريد الالكتروني</t>
-        </is>
-      </c>
-      <c r="Z6" s="454" t="inlineStr">
-        <is>
-          <t xml:space="preserve">الجنسية</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A6:BM46" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="3">
-    <mergeCell ref="H2:R5"/>
-    <mergeCell ref="S4:T4"/>
-    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="H2:S5"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="W4:Y4"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/tpl-gov.xlsx
+++ b/tpl-gov.xlsx
@@ -3326,7 +3326,7 @@
     <col min="20" max="20" width="52.1" style="47" customWidth="1"/>
     <col min="21" max="21" width="56.1" style="166" customWidth="1"/>
     <col min="22" max="22" width="41.5" style="166" customWidth="1"/>
-    <col min="23" max="23" width="10.5" style="47" customWidth="1"/>
+    <col min="23" max="23" width="16.5" style="47" customWidth="1"/>
     <col min="24" max="24" width="17.0" style="47" customWidth="1"/>
     <col min="25" max="25" width="53.7" style="47" customWidth="1"/>
     <col min="26" max="26" width="34.0" style="47" customWidth="1"/>
